--- a/test_data/Book1.xlsx
+++ b/test_data/Book1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -71,13 +71,16 @@
     <t>mobileno</t>
   </si>
   <si>
+    <t>Tanunegi</t>
+  </si>
+  <si>
+    <t>tanunegi@gmail.com</t>
+  </si>
+  <si>
+    <t>tanu@1234</t>
+  </si>
+  <si>
     <t>Tanu</t>
-  </si>
-  <si>
-    <t>tannuuu@gmail.com</t>
-  </si>
-  <si>
-    <t>tanu@1234</t>
   </si>
   <si>
     <t>kansal</t>
@@ -102,7 +105,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,13 +117,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -573,146 +569,146 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1059,7 +1055,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="16.7083333333333" customWidth="1"/>
     <col min="3" max="3" width="18.1416666666667" customWidth="1"/>
@@ -1136,22 +1132,22 @@
         <v>1998</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
       </c>
       <c r="M2">
         <v>101213</v>
@@ -1162,7 +1158,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="tannuuu@gmail.com" tooltip="mailto:tannuuu@gmail.com"/>
+    <hyperlink ref="B2" r:id="rId1" display="tanunegi@gmail.com" tooltip="mailto:tanunegi@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
